--- a/data_modified.xlsx
+++ b/data_modified.xlsx
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Không tìm thấy size</t>
+          <t>Giá đã tăng</t>
         </is>
       </c>
     </row>
@@ -1662,11 +1662,7 @@
       <c r="D48" s="3" t="n">
         <v>33980</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1685,11 +1681,7 @@
       <c r="D49" s="3" t="n">
         <v>31900</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -1708,11 +1700,7 @@
       <c r="D50" s="3" t="n">
         <v>34799</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1729,11 +1717,7 @@
         <v>37</v>
       </c>
       <c r="D51" s="3" t="n"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1752,11 +1736,7 @@
       <c r="D52" s="3" t="n">
         <v>34800</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1775,11 +1755,7 @@
       <c r="D53" s="3" t="n">
         <v>35499</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1798,11 +1774,7 @@
       <c r="D54" s="3" t="n">
         <v>33900</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1823,7 +1795,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Không tìm thấy size</t>
+          <t>Giá đã giảm</t>
         </is>
       </c>
     </row>
@@ -1844,11 +1816,7 @@
       <c r="D56" s="3" t="n">
         <v>44990</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -1867,11 +1835,7 @@
       <c r="D57" s="3" t="n">
         <v>32896</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -1892,7 +1856,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Không tìm thấy size</t>
+          <t>Giá đã giảm</t>
         </is>
       </c>
     </row>
@@ -1913,11 +1877,7 @@
       <c r="D59" s="3" t="n">
         <v>35999</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -1936,11 +1896,7 @@
       <c r="D60" s="3" t="n">
         <v>57999</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1959,11 +1915,7 @@
       <c r="D61" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -1982,11 +1934,7 @@
       <c r="D62" s="3" t="n">
         <v>30900</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -2005,11 +1953,7 @@
       <c r="D63" s="3" t="n">
         <v>38770</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -2028,11 +1972,7 @@
       <c r="D64" s="3" t="n">
         <v>29500</v>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2051,11 +1991,7 @@
       <c r="D65" s="3" t="n">
         <v>34999</v>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -2074,11 +2010,7 @@
       <c r="D66" s="3" t="n">
         <v>55000</v>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2097,11 +2029,7 @@
       <c r="D67" s="3" t="n">
         <v>36499</v>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -2120,11 +2048,7 @@
       <c r="D68" s="3" t="n">
         <v>40999</v>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2143,11 +2067,7 @@
       <c r="D69" s="3" t="n">
         <v>40999</v>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -2168,7 +2088,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Không tìm thấy size</t>
+          <t>Giá đã giảm</t>
         </is>
       </c>
     </row>
@@ -2189,11 +2109,7 @@
       <c r="D71" s="3" t="n">
         <v>58000</v>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Không tìm thấy size</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">

--- a/data_modified.xlsx
+++ b/data_modified.xlsx
@@ -556,7 +556,11 @@
       <c r="D3" t="n">
         <v>13300</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Giá đã giảm</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
@@ -1700,7 +1704,11 @@
       <c r="D50" s="3" t="n">
         <v>34799</v>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Giá đã giảm</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1736,7 +1744,11 @@
       <c r="D52" s="3" t="n">
         <v>34800</v>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Giá đã tăng</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1755,7 +1767,11 @@
       <c r="D53" s="3" t="n">
         <v>35499</v>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Giá đã giảm</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1953,7 +1969,11 @@
       <c r="D63" s="3" t="n">
         <v>38770</v>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Giá đã giảm</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -1991,7 +2011,11 @@
       <c r="D65" s="3" t="n">
         <v>34999</v>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Giá đã giảm</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -2086,11 +2110,7 @@
       <c r="D70" s="3" t="n">
         <v>55555</v>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Giá đã giảm</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -2359,7 +2379,11 @@
       <c r="D83" s="3" t="n">
         <v>13499</v>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Giá đã tăng</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -2443,7 +2467,11 @@
       <c r="D87" s="3" t="n">
         <v>16575</v>
       </c>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Giá đã giảm</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
